--- a/artfynd/A 44336-2023 artfynd.xlsx
+++ b/artfynd/A 44336-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44336-2023 artfynd.xlsx
+++ b/artfynd/A 44336-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112831254</v>
+        <v>112881649</v>
       </c>
       <c r="B2" t="n">
-        <v>78021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862270</v>
+        <v>861886</v>
       </c>
       <c r="R2" t="n">
-        <v>7332089</v>
+        <v>7331668</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,65 +760,71 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112831252</v>
+        <v>112881610</v>
       </c>
       <c r="B3" t="n">
-        <v>91197</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862159</v>
+        <v>861941</v>
       </c>
       <c r="R3" t="n">
-        <v>7331710</v>
+        <v>7331668</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,71 +862,78 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112831256</v>
+        <v>112881612</v>
       </c>
       <c r="B4" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861994</v>
+        <v>861900</v>
       </c>
       <c r="R4" t="n">
-        <v>7331538</v>
+        <v>7331703</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,82 +965,94 @@
           <t>2023-10-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>11 fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Torr-frisk hed med tall</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallhed på frisk mark med friskmossor och inslag av stora block.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112831257</v>
+        <v>112881638</v>
       </c>
       <c r="B5" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862148</v>
+        <v>861909</v>
       </c>
       <c r="R5" t="n">
-        <v>7331748</v>
+        <v>7331684</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,71 +1090,88 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Torr-frisk hed med tall</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallhed på frisk mark med inslag av stora block.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112831259</v>
+        <v>112881642</v>
       </c>
       <c r="B6" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862047</v>
+        <v>861916</v>
       </c>
       <c r="R6" t="n">
-        <v>7331573</v>
+        <v>7331695</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,33 +1209,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112831253</v>
+        <v>112831252</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861876</v>
+        <v>862159</v>
       </c>
       <c r="R7" t="n">
-        <v>7331498</v>
+        <v>7331710</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,37 +1325,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112831251</v>
+        <v>112881617</v>
       </c>
       <c r="B8" t="n">
-        <v>96141</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1360,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862091</v>
+        <v>861962</v>
       </c>
       <c r="R8" t="n">
-        <v>7331617</v>
+        <v>7331716</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,27 +1410,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112831247</v>
+        <v>112831255</v>
       </c>
       <c r="B9" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861980</v>
+        <v>862052</v>
       </c>
       <c r="R9" t="n">
-        <v>7331613</v>
+        <v>7331633</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1474,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,19 +1524,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112831258</v>
+        <v>112831256</v>
       </c>
       <c r="B10" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1541,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862051</v>
+        <v>861994</v>
       </c>
       <c r="R10" t="n">
-        <v>7331603</v>
+        <v>7331538</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1577,6 +1595,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>11 fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,15 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112831248</v>
+        <v>112831257</v>
       </c>
       <c r="B11" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1637,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862238</v>
+        <v>862148</v>
       </c>
       <c r="R11" t="n">
-        <v>7331910</v>
+        <v>7331748</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1679,11 +1697,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,19 +1723,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112831255</v>
+        <v>112831258</v>
       </c>
       <c r="B12" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1750,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>862052</v>
+        <v>862050</v>
       </c>
       <c r="R12" t="n">
-        <v>7331633</v>
+        <v>7331603</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,11 +1794,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>15 fruktkroppar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,15 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112831245</v>
+        <v>112831259</v>
       </c>
       <c r="B13" t="n">
-        <v>56898</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>862085</v>
+        <v>862046</v>
       </c>
       <c r="R13" t="n">
-        <v>7331626</v>
+        <v>7331573</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1919,37 +1917,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112831249</v>
+        <v>112881603</v>
       </c>
       <c r="B14" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1952,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>862238</v>
+        <v>862002</v>
       </c>
       <c r="R14" t="n">
-        <v>7331910</v>
+        <v>7331682</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,49 +2002,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112831250</v>
+        <v>112881604</v>
       </c>
       <c r="B15" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,13 +2049,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>862226</v>
+        <v>862149</v>
       </c>
       <c r="R15" t="n">
-        <v>7331890</v>
+        <v>7331763</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2111,49 +2099,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112881639</v>
+        <v>112881605</v>
       </c>
       <c r="B16" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>861803</v>
+        <v>861895</v>
       </c>
       <c r="R16" t="n">
-        <v>7331572</v>
+        <v>7331731</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,15 +2208,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112881645</v>
+        <v>112881606</v>
       </c>
       <c r="B17" t="n">
-        <v>91249</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2219,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>861912</v>
+        <v>861902</v>
       </c>
       <c r="R17" t="n">
-        <v>7331719</v>
+        <v>7331530</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,15 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112881646</v>
+        <v>112881607</v>
       </c>
       <c r="B18" t="n">
-        <v>91249</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2316,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2340,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>861982</v>
+        <v>861898</v>
       </c>
       <c r="R18" t="n">
-        <v>7331685</v>
+        <v>7331709</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,15 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112881613</v>
+        <v>112881608</v>
       </c>
       <c r="B19" t="n">
-        <v>91249</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,21 +2413,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>861931</v>
+        <v>861939</v>
       </c>
       <c r="R19" t="n">
-        <v>7331695</v>
+        <v>7331707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,15 +2499,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112881601</v>
+        <v>112881619</v>
       </c>
       <c r="B20" t="n">
-        <v>91249</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2510,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2534,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861896</v>
+        <v>862161</v>
       </c>
       <c r="R20" t="n">
-        <v>7331716</v>
+        <v>7331646</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,6 +2578,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2633,61 +2597,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112881638</v>
+        <v>112881622</v>
       </c>
       <c r="B21" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861910</v>
+        <v>861912</v>
       </c>
       <c r="R21" t="n">
-        <v>7331684</v>
+        <v>7331694</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,19 +2676,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Torr-frisk hed med tall</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Tallhed på frisk mark med inslag av stora block.</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2757,37 +2694,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112881624</v>
+        <v>112881623</v>
       </c>
       <c r="B22" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2797,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861967</v>
+        <v>862157</v>
       </c>
       <c r="R22" t="n">
-        <v>7331751</v>
+        <v>7331657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,15 +2791,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112881617</v>
+        <v>112881625</v>
       </c>
       <c r="B23" t="n">
-        <v>91197</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,21 +2802,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2899,10 +2826,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>861962</v>
+        <v>861981</v>
       </c>
       <c r="R23" t="n">
-        <v>7331716</v>
+        <v>7331685</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,19 +2888,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112881603</v>
+        <v>112881636</v>
       </c>
       <c r="B24" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3001,10 +2923,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>862003</v>
+        <v>861932</v>
       </c>
       <c r="R24" t="n">
-        <v>7331682</v>
+        <v>7331711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,15 +2985,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112881637</v>
+        <v>112881641</v>
       </c>
       <c r="B25" t="n">
-        <v>91249</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3079,21 +2996,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3103,10 +3020,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>861975</v>
+        <v>861897</v>
       </c>
       <c r="R25" t="n">
-        <v>7331673</v>
+        <v>7331715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,19 +3082,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112881608</v>
+        <v>112881644</v>
       </c>
       <c r="B26" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3205,10 +3117,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>861939</v>
+        <v>861908</v>
       </c>
       <c r="R26" t="n">
-        <v>7331707</v>
+        <v>7331724</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,6 +3161,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3267,19 +3180,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112881607</v>
+        <v>112881648</v>
       </c>
       <c r="B27" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3307,10 +3215,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>861898</v>
+        <v>861912</v>
       </c>
       <c r="R27" t="n">
-        <v>7331709</v>
+        <v>7331725</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3369,37 +3277,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112881636</v>
+        <v>112881635</v>
       </c>
       <c r="B28" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3409,10 +3312,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>861932</v>
+        <v>861918</v>
       </c>
       <c r="R28" t="n">
-        <v>7331711</v>
+        <v>7331699</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,37 +3374,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112881641</v>
+        <v>112831253</v>
       </c>
       <c r="B29" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3511,13 +3409,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>861897</v>
+        <v>861876</v>
       </c>
       <c r="R29" t="n">
-        <v>7331716</v>
+        <v>7331498</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3561,49 +3459,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112881644</v>
+        <v>112831254</v>
       </c>
       <c r="B30" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3613,13 +3506,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>861908</v>
+        <v>862270</v>
       </c>
       <c r="R30" t="n">
-        <v>7331724</v>
+        <v>7332089</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3657,34 +3550,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112881625</v>
+        <v>112831247</v>
       </c>
       <c r="B31" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3692,21 +3579,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3716,13 +3603,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>861982</v>
+        <v>861979</v>
       </c>
       <c r="R31" t="n">
-        <v>7331685</v>
+        <v>7331613</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3752,6 +3639,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3766,49 +3658,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112881629</v>
+        <v>112831248</v>
       </c>
       <c r="B32" t="n">
-        <v>56879</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103035</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3818,13 +3705,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>861976</v>
+        <v>862237</v>
       </c>
       <c r="R32" t="n">
-        <v>7331610</v>
+        <v>7331909</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3854,6 +3741,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3868,73 +3760,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112881642</v>
+        <v>112881616</v>
       </c>
       <c r="B33" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1958</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>861917</v>
+        <v>861816</v>
       </c>
       <c r="R33" t="n">
-        <v>7331694</v>
+        <v>7331579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3975,7 +3851,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3994,19 +3869,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112881628</v>
+        <v>112881618</v>
       </c>
       <c r="B34" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4034,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>861899</v>
+        <v>861805</v>
       </c>
       <c r="R34" t="n">
-        <v>7331689</v>
+        <v>7331567</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4096,19 +3966,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112881616</v>
+        <v>112881628</v>
       </c>
       <c r="B35" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4136,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>861816</v>
+        <v>861899</v>
       </c>
       <c r="R35" t="n">
-        <v>7331579</v>
+        <v>7331689</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4198,15 +4063,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112881648</v>
+        <v>112881630</v>
       </c>
       <c r="B36" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4214,21 +4074,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4098,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>861912</v>
+        <v>861884</v>
       </c>
       <c r="R36" t="n">
-        <v>7331724</v>
+        <v>7331671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4300,15 +4160,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112881606</v>
+        <v>112881640</v>
       </c>
       <c r="B37" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4316,21 +4171,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4340,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>861903</v>
+        <v>861888</v>
       </c>
       <c r="R37" t="n">
-        <v>7331530</v>
+        <v>7331682</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4402,15 +4257,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112881618</v>
+        <v>112831245</v>
       </c>
       <c r="B38" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4418,21 +4268,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4442,13 +4292,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>861805</v>
+        <v>862085</v>
       </c>
       <c r="R38" t="n">
-        <v>7331567</v>
+        <v>7331626</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4492,27 +4342,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112881640</v>
+        <v>112881609</v>
       </c>
       <c r="B39" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4520,21 +4365,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4544,10 +4389,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>861889</v>
+        <v>861974</v>
       </c>
       <c r="R39" t="n">
-        <v>7331682</v>
+        <v>7331696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,37 +4451,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112881635</v>
+        <v>112881629</v>
       </c>
       <c r="B40" t="n">
-        <v>91248</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>205976</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4646,10 +4486,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>861918</v>
+        <v>861975</v>
       </c>
       <c r="R40" t="n">
-        <v>7331700</v>
+        <v>7331609</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,64 +4548,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112881610</v>
+        <v>112831251</v>
       </c>
       <c r="B41" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1958</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>861942</v>
+        <v>862091</v>
       </c>
       <c r="R41" t="n">
-        <v>7331668</v>
+        <v>7331617</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4803,83 +4627,66 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112881612</v>
+        <v>112831249</v>
       </c>
       <c r="B42" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1958</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Börjelsbyn, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>861900</v>
+        <v>862237</v>
       </c>
       <c r="R42" t="n">
-        <v>7331704</v>
+        <v>7331909</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4917,66 +4724,50 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Torr-frisk hed med tall</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Tallhed på frisk mark med friskmossor och inslag av stora block.</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112881609</v>
+        <v>112831250</v>
       </c>
       <c r="B43" t="n">
-        <v>56898</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4986,13 +4777,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>861975</v>
+        <v>862225</v>
       </c>
       <c r="R43" t="n">
-        <v>7331696</v>
+        <v>7331890</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5036,27 +4827,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112881622</v>
+        <v>112881602</v>
       </c>
       <c r="B44" t="n">
-        <v>91205</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5064,21 +4850,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5088,10 +4874,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>861912</v>
+        <v>861923</v>
       </c>
       <c r="R44" t="n">
-        <v>7331694</v>
+        <v>7331673</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5150,15 +4936,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112881602</v>
+        <v>112881611</v>
       </c>
       <c r="B45" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5190,10 +4971,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>861924</v>
+        <v>861929</v>
       </c>
       <c r="R45" t="n">
-        <v>7331673</v>
+        <v>7331733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5252,15 +5033,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112881611</v>
+        <v>112881621</v>
       </c>
       <c r="B46" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5292,10 +5068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>861929</v>
+        <v>862090</v>
       </c>
       <c r="R46" t="n">
-        <v>7331734</v>
+        <v>7331722</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5354,15 +5130,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112881621</v>
+        <v>112881624</v>
       </c>
       <c r="B47" t="n">
-        <v>96135</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5394,10 +5165,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>862090</v>
+        <v>861966</v>
       </c>
       <c r="R47" t="n">
-        <v>7331722</v>
+        <v>7331751</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5453,6 +5224,103 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>112881639</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Börjelsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>861803</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7331572</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
